--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Qua kết quả học tập Quý 1, em Lò Mai Phương Chi còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần biểu thức toạ độ của các phép toán vectơ là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Chi Mai còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần biểu thức toạ độ của các phép toán vectơ là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Đức Huy còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần biểu thức toạ độ của các phép toán vectơ là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Minh Đức bị hổng khá nhiều kiến thức nền, ảnh hưởng trực tiếp đến kết quả các bài kiểm tra. Tuy nhiên phần biểu thức toạ độ của các phép toán vectơ em còn mất căn bản, cần học lại từ khái niệm trước khi luyện bài tập. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Thành Trung bị hổng khá nhiều kiến thức nền, ảnh hưởng trực tiếp đến kết quả các bài kiểm tra. Tuy nhiên phần biểu thức toạ độ của các phép toán vectơ em còn mất căn bản, cần học lại từ khái niệm trước khi luyện bài tập. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trần Bảo Lâm đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em học tốt nhất ở phần sự đồng biến, nghịch biến của hàm số, nắm được cách làm các dạng cơ bản. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần sự đồng biến, nghịch biến của hàm số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trần Đặng Tuấn Nam còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần biểu thức toạ độ của các phép toán vectơ là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trương Lê Bình Minh còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần biểu thức toạ độ của các phép toán vectơ là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần sự đồng biến, nghịch biến của hàm số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung sự đồng biến, nghịch biến của hàm số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần sự đồng biến, nghịch biến của hàm số. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần biểu thức toạ độ của các phép toán vectơ trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -460,13 +460,13 @@
         <v>Lò Mai Phương Chi</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Nữ</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -480,13 +480,13 @@
         <v>Nguyễn Chi Mai</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Nữ</v>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -500,13 +500,13 @@
         <v>Nguyễn Đức Huy</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -520,13 +520,13 @@
         <v>Nguyễn Minh Đức</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -540,13 +540,13 @@
         <v>Nguyễn Thành Trung</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -560,13 +560,13 @@
         <v>Trần Bảo Lâm</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung sự đồng biến, nghịch biến của hàm số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -580,13 +580,13 @@
         <v>Trần Đặng Tuấn Nam</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -600,13 +600,13 @@
         <v>Trương Lê Bình Minh</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>Nam</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Lỗi của em rải ở nhiều dạng khác nhau chứ không tập trung vào một phần kiến thức nào, cho thấy em cần rà soát kỹ hơn sau mỗi bài làm. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, còn chọn chưa đúng đáp án ở một số câu trắc nghiệm. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Lỗi của em rải ở nhiều dạng khác nhau chứ không tập trung vào một phần kiến thức nào, cho thấy em cần rà soát kỹ hơn sau mỗi bài làm. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F12" t="str">
         <v/>

--- a/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
+++ b/docs/qa/12LoTrinh1_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Lò Mai Phương Chi đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lò Mai Phương Chi bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Nguyễn Chi Mai đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Chi Mai bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Nguyễn Đức Huy đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Đức Huy bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Nguyễn Minh Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Minh Đức bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, phần lớn lỗi nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Nguyễn Thành Trung đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Thành Trung bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, còn chọn chưa đúng đáp án ở một số câu trắc nghiệm. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
+        <v>Trong Quý 1, em Trần Bảo Lâm đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, còn chọn chưa đúng đáp án ở một số câu trắc nghiệm. Em thực hiện tốt các dạng bài của sự đồng biến, nghịch biến của hàm số.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Trần Đặng Tuấn Nam đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Đặng Tuấn Nam bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Trương Lê Bình Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trương Lê Bình Minh bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở sự đồng biến, nghịch biến của hàm số. Nội dung biểu thức toạ độ của các phép toán vectơ cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F12" t="str">
         <v/>
